--- a/九龙-旺角-利奥坊．凯岸/利奥坊．凯岸_销控明细表.xlsx
+++ b/九龙-旺角-利奥坊．凯岸/利奥坊．凯岸_销控明细表.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -835,7 +835,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -897,7 +897,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
+          <t>2022-09-23</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2021-10-27</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2021-11-29</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2021-11-29</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2021-11-18</t>
+          <t>2021-11-19</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2023-03-09</t>
+          <t>2023-03-10</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
+          <t>2021-10-08</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2021-07-21</t>
+          <t>2021-07-22</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2021-08-08</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2021-11-15</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-11-10</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2021-11-12</t>
+          <t>2021-11-13</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2021-06-28</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2021-08-03</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2023-11-30</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2018-07-06</t>
+          <t>2018-07-07</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2018-07-16</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2018-08-21</t>
+          <t>2018-08-22</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2018-07-18</t>
+          <t>2018-07-19</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2018-07-18</t>
+          <t>2018-07-19</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2018-07-18</t>
+          <t>2018-07-19</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2018-07-23</t>
+          <t>2018-07-24</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2018-07-12</t>
+          <t>2018-07-13</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-17</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2018-07-26</t>
+          <t>2018-07-27</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2018-07-18</t>
+          <t>2018-07-19</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2018-07-11</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2018-07-22</t>
+          <t>2018-07-23</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2018-07-08</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2018-06-15</t>
+          <t>2018-06-16</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2018-07-08</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2018-07-16</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
+          <t>2022-02-25</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2021-10-16</t>
+          <t>2021-10-17</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2018-07-16</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2018-07-12</t>
+          <t>2018-07-13</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2018-07-26</t>
+          <t>2018-07-27</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2018-07-12</t>
+          <t>2018-07-13</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2018-07-11</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2022-05-11</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2021-10-19</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2018-07-25</t>
+          <t>2018-07-26</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2018-07-12</t>
+          <t>2018-07-13</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2018-06-22</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2022-12-21</t>
+          <t>2022-12-22</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2023-06-04</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2018-07-25</t>
+          <t>2018-07-26</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2018-07-12</t>
+          <t>2018-07-13</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2018-07-02</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2018-07-12</t>
+          <t>2018-07-13</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2018-10-22</t>
+          <t>2018-10-23</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2018-07-12</t>
+          <t>2018-07-13</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2018-07-30</t>
+          <t>2018-07-31</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2018-06-15</t>
+          <t>2018-06-16</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2018-07-16</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2018-09-05</t>
+          <t>2018-09-06</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2019-08-15</t>
+          <t>2019-08-16</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2018-07-18</t>
+          <t>2018-07-19</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2023-07-31</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2018-06-15</t>
+          <t>2018-06-16</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2018-07-18</t>
+          <t>2018-07-19</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2018-07-12</t>
+          <t>2018-07-13</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2023-04-10</t>
+          <t>2023-04-11</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2018-06-15</t>
+          <t>2018-06-16</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2018-07-09</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2018-07-11</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2018-07-12</t>
+          <t>2018-07-13</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2018-06-22</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2018-07-11</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2018-07-15</t>
+          <t>2018-07-16</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8593,7 +8593,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2023-04-13</t>
+          <t>2023-04-14</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2018-08-27</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2018-07-09</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2018-07-08</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2018-07-12</t>
+          <t>2018-07-13</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2018-07-08</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2018-07-16</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2018-07-08</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2018-08-24</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2018-07-09</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -9895,7 +9895,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2018-06-22</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2023-05-14</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10019,7 +10019,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2018-07-11</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10081,7 +10081,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2018-07-11</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2018-07-09</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10205,7 +10205,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2018-07-11</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2018-07-12</t>
+          <t>2018-07-13</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10453,7 +10453,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10515,7 +10515,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2018-07-12</t>
+          <t>2018-07-13</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2018-07-02</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10887,7 +10887,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2018-07-09</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11197,7 +11197,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2018-07-09</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11259,7 +11259,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2023-04-11</t>
+          <t>2023-04-12</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2018-07-09</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2018-06-15</t>
+          <t>2018-06-16</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2018-09-03</t>
+          <t>2018-09-04</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11755,7 +11755,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2018-07-16</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -11941,7 +11941,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2018-07-16</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2018-07-16</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12065,7 +12065,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2018-07-09</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12251,7 +12251,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12313,7 +12313,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2018-07-02</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12375,7 +12375,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2018-08-21</t>
+          <t>2018-08-22</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2018-07-02</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2018-07-02</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2018-07-08</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12623,7 +12623,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2018-07-16</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12685,7 +12685,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12747,7 +12747,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2018-07-12</t>
+          <t>2018-07-13</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -12933,7 +12933,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -12995,7 +12995,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13057,7 +13057,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2018-07-15</t>
+          <t>2018-07-16</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13181,7 +13181,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2019-07-09</t>
+          <t>2019-07-10</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13243,7 +13243,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13367,7 +13367,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13429,7 +13429,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2018-06-15</t>
+          <t>2018-06-16</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13553,7 +13553,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13615,7 +13615,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2018-07-16</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13677,7 +13677,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13739,7 +13739,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13801,7 +13801,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -13925,7 +13925,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2018-07-18</t>
+          <t>2018-07-19</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -13987,7 +13987,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2018-07-11</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2018-07-15</t>
+          <t>2018-07-16</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14173,7 +14173,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2018-06-15</t>
+          <t>2018-06-16</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14235,7 +14235,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14297,7 +14297,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2018-07-11</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14359,7 +14359,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2018-07-11</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14483,7 +14483,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14545,7 +14545,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2018-06-15</t>
+          <t>2018-06-16</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14607,7 +14607,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14669,7 +14669,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2018-07-23</t>
+          <t>2018-07-24</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -14855,7 +14855,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -14917,7 +14917,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -14979,7 +14979,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2018-06-22</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2018-06-15</t>
+          <t>2018-06-16</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15227,7 +15227,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2018-07-09</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15413,7 +15413,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15475,7 +15475,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15537,7 +15537,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2018-07-11</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15723,7 +15723,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15785,7 +15785,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -15847,7 +15847,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -15909,7 +15909,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -15971,7 +15971,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2018-09-11</t>
+          <t>2018-09-12</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2022-07-13</t>
+          <t>2022-07-14</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16095,7 +16095,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16157,7 +16157,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16219,7 +16219,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16281,7 +16281,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
+          <t>2022-09-23</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16343,7 +16343,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16405,7 +16405,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16529,7 +16529,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2022-01-17</t>
+          <t>2022-01-18</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16591,7 +16591,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -16715,7 +16715,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
+          <t>2022-10-31</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -16847,7 +16847,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
+          <t>2021-08-02</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -16909,7 +16909,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -16971,7 +16971,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2022-04-25</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17095,7 +17095,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2018-09-27</t>
+          <t>2018-09-28</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17157,7 +17157,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2021-12-20</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2021-11-29</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17281,7 +17281,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2021-11-15</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17343,7 +17343,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2023-04-10</t>
+          <t>2023-04-11</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17405,7 +17405,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2018-09-05</t>
+          <t>2018-09-06</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17467,7 +17467,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2018-07-11</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -17529,7 +17529,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2018-07-18</t>
+          <t>2018-07-19</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17591,7 +17591,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
+          <t>2023-12-07</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -17653,7 +17653,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -17715,7 +17715,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2022-03-02</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -17777,7 +17777,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2018-09-13</t>
+          <t>2018-09-14</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -17839,7 +17839,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2021-11-10</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -17901,7 +17901,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-12-02</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -17963,7 +17963,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2021-11-04</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18025,7 +18025,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2018-08-16</t>
+          <t>2018-08-17</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18149,7 +18149,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2018-07-12</t>
+          <t>2018-07-13</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -18211,7 +18211,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2018-07-12</t>
+          <t>2018-07-13</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -18273,7 +18273,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2019-05-22</t>
+          <t>2019-05-23</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -18335,7 +18335,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -18397,7 +18397,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2018-08-15</t>
+          <t>2018-08-16</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -18459,7 +18459,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -18521,7 +18521,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -18583,7 +18583,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -18645,7 +18645,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -18707,7 +18707,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2021-10-22</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -18769,7 +18769,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -18831,7 +18831,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -18893,7 +18893,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2018-07-24</t>
+          <t>2018-07-25</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -18955,7 +18955,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2018-07-18</t>
+          <t>2018-07-19</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -19017,7 +19017,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
+          <t>2018-06-09</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2023-03-08</t>
+          <t>2023-03-09</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -19141,7 +19141,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -19203,7 +19203,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
+          <t>2018-06-09</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -19327,7 +19327,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2018-06-25</t>
+          <t>2018-06-26</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2019-06-19</t>
+          <t>2019-06-20</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -19451,7 +19451,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2018-06-30</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -19513,7 +19513,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -19575,7 +19575,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2018-06-24</t>
+          <t>2018-06-25</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -19637,7 +19637,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -19699,7 +19699,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -19761,7 +19761,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2018-08-14</t>
+          <t>2018-08-15</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -19823,7 +19823,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -19885,7 +19885,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -20009,7 +20009,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -20071,7 +20071,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2018-08-21</t>
+          <t>2018-08-22</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -20195,7 +20195,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
+          <t>2018-06-09</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -20257,7 +20257,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -20319,7 +20319,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2018-07-09</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -20381,7 +20381,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -20443,7 +20443,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2018-07-26</t>
+          <t>2018-07-27</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -20505,7 +20505,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -20567,7 +20567,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -20629,7 +20629,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -20691,7 +20691,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -20753,7 +20753,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2018-08-14</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -20815,7 +20815,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -21001,7 +21001,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -21063,7 +21063,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -21125,7 +21125,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2018-07-08</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -21187,7 +21187,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -21249,7 +21249,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -21311,7 +21311,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -21373,7 +21373,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -21435,7 +21435,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2018-07-16</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -21497,7 +21497,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -21559,7 +21559,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -21621,7 +21621,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -21683,7 +21683,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -21745,7 +21745,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2018-07-02</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -21807,7 +21807,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2018-07-02</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -21931,7 +21931,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2018-07-09</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -21993,7 +21993,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -22055,7 +22055,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2018-06-26</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -22117,7 +22117,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2018-07-18</t>
+          <t>2018-07-19</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -22179,7 +22179,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2018-07-02</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -22241,7 +22241,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -22303,7 +22303,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2018-07-08</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -22365,7 +22365,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2018-07-18</t>
+          <t>2018-07-19</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -22427,7 +22427,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -22489,7 +22489,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -22551,7 +22551,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -22613,7 +22613,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -22675,7 +22675,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2018-06-25</t>
+          <t>2018-06-26</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -22737,7 +22737,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -22799,7 +22799,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2018-08-20</t>
+          <t>2018-08-21</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -22861,7 +22861,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -22923,7 +22923,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -22985,7 +22985,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -23047,7 +23047,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -23109,7 +23109,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -23171,7 +23171,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2018-07-11</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -23295,7 +23295,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
+          <t>2018-06-09</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -23357,7 +23357,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -23419,7 +23419,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -23481,7 +23481,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2018-06-22</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -23543,7 +23543,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -23667,7 +23667,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2018-06-24</t>
+          <t>2018-06-25</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -23729,7 +23729,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -23791,7 +23791,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -23915,7 +23915,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -23977,7 +23977,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -24039,7 +24039,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -24101,7 +24101,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -24163,7 +24163,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2018-07-18</t>
+          <t>2018-07-19</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -24225,7 +24225,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -24287,7 +24287,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2018-07-29</t>
+          <t>2018-07-30</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -24349,7 +24349,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -24411,7 +24411,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
@@ -24473,7 +24473,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2018-07-11</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -24535,7 +24535,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -24597,7 +24597,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
@@ -24659,7 +24659,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -24721,7 +24721,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
+          <t>2018-06-09</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -24783,7 +24783,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -24845,7 +24845,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -24907,7 +24907,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -24969,7 +24969,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2018-06-26</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -25031,7 +25031,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -25093,7 +25093,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -25155,7 +25155,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -25217,7 +25217,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -25279,7 +25279,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2018-06-24</t>
+          <t>2018-06-25</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -25341,7 +25341,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
@@ -25403,7 +25403,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H400" s="5" t="n">
@@ -25465,7 +25465,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
+          <t>2018-06-09</t>
         </is>
       </c>
       <c r="H401" s="5" t="n">
@@ -25527,7 +25527,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H402" s="5" t="n">
@@ -25589,7 +25589,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -25651,7 +25651,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
@@ -25713,7 +25713,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H405" s="5" t="n">
@@ -25775,7 +25775,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -25837,7 +25837,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H407" s="5" t="n">
@@ -25899,7 +25899,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2018-06-27</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H408" s="5" t="n">
@@ -25961,7 +25961,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H409" s="5" t="n">
@@ -26023,7 +26023,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2018-06-26</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="H410" s="5" t="n">
@@ -26085,7 +26085,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2018-06-27</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H411" s="5" t="n">
@@ -26147,7 +26147,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2018-06-27</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H412" s="5" t="n">
@@ -26209,7 +26209,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2018-06-15</t>
+          <t>2018-06-16</t>
         </is>
       </c>
       <c r="H413" s="5" t="n">
@@ -26271,7 +26271,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2018-06-27</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H414" s="5" t="n">
@@ -26333,7 +26333,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H415" s="5" t="n">
@@ -26395,7 +26395,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2018-06-15</t>
+          <t>2018-06-16</t>
         </is>
       </c>
       <c r="H416" s="5" t="n">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H417" s="5" t="n">
@@ -26519,7 +26519,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H418" s="5" t="n">
@@ -26581,7 +26581,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H419" s="5" t="n">
@@ -26643,7 +26643,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H420" s="5" t="n">
@@ -26705,7 +26705,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2018-06-25</t>
+          <t>2018-06-26</t>
         </is>
       </c>
       <c r="H421" s="5" t="n">
@@ -26767,7 +26767,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H422" s="5" t="n">
@@ -26829,7 +26829,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2018-06-27</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H423" s="5" t="n">
@@ -26891,7 +26891,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H424" s="5" t="n">
@@ -26953,7 +26953,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2018-07-02</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H425" s="5" t="n">
@@ -27015,7 +27015,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H426" s="5" t="n">
@@ -27077,7 +27077,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H427" s="5" t="n">
@@ -27139,7 +27139,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
+          <t>2018-06-09</t>
         </is>
       </c>
       <c r="H428" s="5" t="n">
@@ -27201,7 +27201,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2018-06-25</t>
+          <t>2018-06-26</t>
         </is>
       </c>
       <c r="H429" s="5" t="n">
@@ -27263,7 +27263,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H430" s="5" t="n">
@@ -27325,7 +27325,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H431" s="5" t="n">
@@ -27387,7 +27387,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2018-06-27</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H432" s="5" t="n">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
+          <t>2018-06-09</t>
         </is>
       </c>
       <c r="H433" s="5" t="n">
@@ -27511,7 +27511,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H434" s="5" t="n">
@@ -27573,7 +27573,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H435" s="5" t="n">
@@ -27635,7 +27635,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H436" s="5" t="n">
@@ -27697,7 +27697,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2018-07-02</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H437" s="5" t="n">
@@ -27759,7 +27759,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2018-06-25</t>
+          <t>2018-06-26</t>
         </is>
       </c>
       <c r="H438" s="5" t="n">
@@ -27821,7 +27821,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2018-06-26</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="H439" s="5" t="n">
@@ -27883,7 +27883,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
+          <t>2018-06-09</t>
         </is>
       </c>
       <c r="H440" s="5" t="n">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H441" s="5" t="n">
@@ -28007,7 +28007,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H442" s="5" t="n">
@@ -28069,7 +28069,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
+          <t>2018-06-09</t>
         </is>
       </c>
       <c r="H443" s="5" t="n">
@@ -28131,7 +28131,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2018-06-27</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H444" s="5" t="n">
@@ -28193,7 +28193,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H445" s="5" t="n">
@@ -28255,7 +28255,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H446" s="5" t="n">
@@ -28317,7 +28317,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H447" s="5" t="n">
@@ -28379,7 +28379,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H448" s="5" t="n">
@@ -28441,7 +28441,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2018-06-26</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="H449" s="5" t="n">
@@ -28503,7 +28503,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2018-06-27</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H450" s="5" t="n">
@@ -28565,7 +28565,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
+          <t>2018-06-09</t>
         </is>
       </c>
       <c r="H451" s="5" t="n">
@@ -28627,7 +28627,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2018-06-21</t>
+          <t>2018-06-22</t>
         </is>
       </c>
       <c r="H452" s="5" t="n">
@@ -28689,7 +28689,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H453" s="5" t="n">
@@ -28751,7 +28751,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H454" s="5" t="n">
@@ -28813,7 +28813,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2018-06-24</t>
+          <t>2018-06-25</t>
         </is>
       </c>
       <c r="H455" s="5" t="n">
@@ -28875,7 +28875,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H456" s="5" t="n">
@@ -28937,7 +28937,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2018-10-10</t>
+          <t>2018-10-11</t>
         </is>
       </c>
       <c r="H457" s="5" t="n">
@@ -28999,7 +28999,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2018-06-27</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H458" s="5" t="n">
@@ -29061,7 +29061,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H459" s="5" t="n">
@@ -29123,7 +29123,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H460" s="5" t="n">
@@ -29185,7 +29185,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2018-06-20</t>
+          <t>2018-06-21</t>
         </is>
       </c>
       <c r="H461" s="5" t="n">
@@ -29247,7 +29247,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2018-06-25</t>
+          <t>2018-06-26</t>
         </is>
       </c>
       <c r="H462" s="5" t="n">
@@ -29309,7 +29309,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H463" s="5" t="n">
@@ -29371,7 +29371,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H464" s="5" t="n">
@@ -29433,7 +29433,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H465" s="5" t="n">
@@ -29495,7 +29495,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H466" s="5" t="n">
@@ -29557,7 +29557,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2018-07-02</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H467" s="5" t="n">
@@ -29619,7 +29619,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H468" s="5" t="n">
@@ -29681,7 +29681,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H469" s="5" t="n">
@@ -29743,7 +29743,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2018-07-02</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H470" s="5" t="n">
@@ -29805,7 +29805,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H471" s="5" t="n">
@@ -29867,7 +29867,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H472" s="5" t="n">
@@ -29929,7 +29929,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H473" s="5" t="n">
@@ -29991,7 +29991,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2018-07-02</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H474" s="5" t="n">
@@ -30053,7 +30053,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H475" s="5" t="n">
@@ -30115,7 +30115,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
+          <t>2018-06-09</t>
         </is>
       </c>
       <c r="H476" s="5" t="n">
@@ -30177,7 +30177,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H477" s="5" t="n">
@@ -30239,7 +30239,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H478" s="5" t="n">
@@ -30301,7 +30301,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2018-06-27</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H479" s="5" t="n">
@@ -30363,7 +30363,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
+          <t>2018-06-09</t>
         </is>
       </c>
       <c r="H480" s="5" t="n">
@@ -30425,7 +30425,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2018-07-02</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H481" s="5" t="n">
@@ -30487,7 +30487,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2018-06-25</t>
+          <t>2018-06-26</t>
         </is>
       </c>
       <c r="H482" s="5" t="n">
@@ -30549,7 +30549,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2018-06-25</t>
+          <t>2018-06-26</t>
         </is>
       </c>
       <c r="H483" s="5" t="n">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H484" s="5" t="n">
@@ -30673,7 +30673,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H485" s="5" t="n">
@@ -30735,7 +30735,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H486" s="5" t="n">
@@ -30797,7 +30797,7 @@
       </c>
       <c r="G487" s="3" t="inlineStr">
         <is>
-          <t>2018-07-02</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H487" s="5" t="n">
@@ -30859,7 +30859,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H488" s="5" t="n">
@@ -30921,7 +30921,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H489" s="5" t="n">
@@ -30983,7 +30983,7 @@
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H490" s="5" t="n">
@@ -31045,7 +31045,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H491" s="5" t="n">
@@ -31107,7 +31107,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H492" s="5" t="n">
@@ -31169,7 +31169,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2018-06-24</t>
+          <t>2018-06-25</t>
         </is>
       </c>
       <c r="H493" s="5" t="n">
@@ -31231,7 +31231,7 @@
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
+          <t>2018-06-09</t>
         </is>
       </c>
       <c r="H494" s="5" t="n">
@@ -31293,7 +31293,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H495" s="5" t="n">
@@ -31355,7 +31355,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H496" s="5" t="n">
@@ -31417,7 +31417,7 @@
       </c>
       <c r="G497" s="3" t="inlineStr">
         <is>
-          <t>2018-07-02</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H497" s="5" t="n">
@@ -31479,7 +31479,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H498" s="5" t="n">
@@ -31541,7 +31541,7 @@
       </c>
       <c r="G499" s="3" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
+          <t>2018-06-09</t>
         </is>
       </c>
       <c r="H499" s="5" t="n">
@@ -31603,7 +31603,7 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H500" s="5" t="n">
@@ -31665,7 +31665,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
+          <t>2018-06-09</t>
         </is>
       </c>
       <c r="H501" s="5" t="n">
@@ -31727,7 +31727,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>2018-06-28</t>
+          <t>2018-06-29</t>
         </is>
       </c>
       <c r="H502" s="5" t="n">
@@ -31789,7 +31789,7 @@
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>2018-07-08</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="H503" s="5" t="n">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2018-07-06</t>
         </is>
       </c>
       <c r="H504" s="5" t="n">
@@ -31913,7 +31913,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2018-07-09</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H505" s="5" t="n">
@@ -31975,7 +31975,7 @@
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="H506" s="5" t="n">
@@ -32037,7 +32037,7 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2023-04-21</t>
         </is>
       </c>
       <c r="H507" s="5" t="n">
@@ -32099,7 +32099,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2018-08-06</t>
+          <t>2018-08-07</t>
         </is>
       </c>
       <c r="H508" s="5" t="n">
@@ -32161,7 +32161,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="H509" s="5" t="n">
@@ -32223,7 +32223,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="H510" s="5" t="n">
@@ -32285,7 +32285,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2023-03-15</t>
+          <t>2023-03-16</t>
         </is>
       </c>
       <c r="H511" s="5" t="n">
@@ -32347,7 +32347,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="H512" s="5" t="n">
@@ -32409,7 +32409,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H513" s="5" t="n">
@@ -32471,7 +32471,7 @@
       </c>
       <c r="G514" s="3" t="inlineStr">
         <is>
-          <t>2021-08-19</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="H514" s="5" t="n">
@@ -32533,7 +32533,7 @@
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>2021-08-02</t>
+          <t>2021-08-03</t>
         </is>
       </c>
       <c r="H515" s="5" t="n">
@@ -32595,7 +32595,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2019-11-03</t>
+          <t>2019-11-04</t>
         </is>
       </c>
       <c r="H516" s="5" t="n">
@@ -32810,7 +32810,7 @@
           <t>B | 508呎 (3房)
 $1708万
 $33,622/呎
-(22年-09月-22日)</t>
+(22年-09月-23日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -32818,7 +32818,7 @@
           <t>C | 509呎 (3房)
 $1300万
 $25,540/呎
-(24年-06月-18日)</t>
+(24年-06月-19日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -32826,7 +32826,7 @@
           <t>D | 579呎 (3房)
 $1388万
 $23,972/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr"/>
@@ -32848,7 +32848,7 @@
           <t>A | 417呎 (2房)
 $1079万
 $25,877/呎
-(23年-07月-18日)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -32856,7 +32856,7 @@
           <t>B | 251呎 (1房)
 $736万
 $29,341/呎
-(21年-08月-08日)</t>
+(21年-08月-09日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -32864,7 +32864,7 @@
           <t>C | 252呎 (1房)
 $746万
 $29,589/呎
-(21年-07月-21日)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -32872,7 +32872,7 @@
           <t>D | 198呎 (开放式)
 $638万
 $32,227/呎
-(21年-10月-07日)</t>
+(21年-10月-08日)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -32880,7 +32880,7 @@
           <t>E | 309呎 (1房)
 $801万
 $25,934/呎
-(23年-03月-09日)</t>
+(23年-03月-10日)</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -32888,7 +32888,7 @@
           <t>F | 253呎 (1房)
 $705万
 $27,861/呎
-(21年-11月-18日)</t>
+(21年-11月-19日)</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -32896,7 +32896,7 @@
           <t>G | 194呎 (开放式)
 $448万
 $23,088/呎
-(23年-09月-28日)</t>
+(23年-09月-29日)</t>
         </is>
       </c>
       <c r="I6" s="21" t="inlineStr">
@@ -32904,7 +32904,7 @@
           <t>H | 249呎 (1房)
 $698万
 $28,012/呎
-(21年-11月-29日)</t>
+(21年-11月-30日)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
@@ -32912,7 +32912,7 @@
           <t>J | 249呎 (1房)
 $693万
 $27,849/呎
-(21年-11月-29日)</t>
+(21年-11月-30日)</t>
         </is>
       </c>
       <c r="K6" s="21" t="inlineStr">
@@ -32920,7 +32920,7 @@
           <t>K | 278呎 (1房)
 $576万
 $20,730/呎
-(24年-03月-17日)</t>
+(24年-03月-18日)</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
@@ -32928,7 +32928,7 @@
           <t>L | 193呎 (开放式)
 $605万
 $31,332/呎
-(21年-10月-27日)</t>
+(21年-10月-28日)</t>
         </is>
       </c>
     </row>
@@ -32943,7 +32943,7 @@
           <t>A | 417呎 (2房)
 $986万
 $23,646/呎
-(23年-11月-30日)</t>
+(23年-12月-01日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -32951,7 +32951,7 @@
           <t>B | 251呎 (1房)
 $727万
 $28,983/呎
-(21年-08月-03日)</t>
+(21年-08月-04日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -32959,7 +32959,7 @@
           <t>C | 252呎 (1房)
 $745万
 $29,557/呎
-(21年-06月-28日)</t>
+(21年-06月-29日)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -32967,7 +32967,7 @@
           <t>D | 198呎 (开放式)
 $637万
 $32,181/呎
-(21年-10月-14日)</t>
+(21年-10月-15日)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -32975,7 +32975,7 @@
           <t>E | 309呎 (1房)
 $899万
 $29,091/呎
-(21年-11月-12日)</t>
+(21年-11月-13日)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -32983,7 +32983,7 @@
           <t>F | 253呎 (1房)
 $696万
 $27,523/呎
-(21年-11月-09日)</t>
+(21年-11月-10日)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -32991,7 +32991,7 @@
           <t>G | 194呎 (开放式)
 $485万
 $25,019/呎
-(23年-04月-17日)</t>
+(23年-04月-18日)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -32999,7 +32999,7 @@
           <t>H | 249呎 (1房)
 $696万
 $27,969/呎
-(21年-10月-14日)</t>
+(21年-10月-15日)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -33007,7 +33007,7 @@
           <t>J | 249呎 (1房)
 $692万
 $27,801/呎
-(21年-10月-11日)</t>
+(21年-10月-12日)</t>
         </is>
       </c>
       <c r="K7" s="21" t="inlineStr">
@@ -33015,7 +33015,7 @@
           <t>K | 278呎 (1房)
 $569万
 $20,471/呎
-(24年-03月-24日)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -33023,7 +33023,7 @@
           <t>L | 193呎 (开放式)
 $597万
 $30,936/呎
-(21年-11月-15日)</t>
+(21年-11月-16日)</t>
         </is>
       </c>
     </row>
@@ -33038,7 +33038,7 @@
           <t>A | 417呎 (2房)
 $1173万
 $28,122/呎
-(18年-07月-18日)</t>
+(18年-07月-19日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -33046,7 +33046,7 @@
           <t>B | 251呎 (1房)
 $722万
 $28,773/呎
-(18年-07月-18日)</t>
+(18年-07月-19日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -33054,7 +33054,7 @@
           <t>C | 252呎 (1房)
 $724万
 $28,738/呎
-(18年-07月-18日)</t>
+(18年-07月-19日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -33062,7 +33062,7 @@
           <t>D | 198呎 (开放式)
 $643万
 $32,475/呎
-(18年-08月-21日)</t>
+(18年-08月-22日)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -33070,7 +33070,7 @@
           <t>E | 309呎 (1房)
 $863万
 $27,915/呎
-(21年-09月-13日)</t>
+(21年-09月-14日)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -33078,7 +33078,7 @@
           <t>F | 253呎 (1房)
 $704万
 $27,832/呎
-(18年-07月-16日)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -33086,7 +33086,7 @@
           <t>G | 194呎 (开放式)
 $535万
 $27,589/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr">
@@ -33094,7 +33094,7 @@
           <t>H | 249呎 (1房)
 $685万
 $27,510/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
@@ -33102,7 +33102,7 @@
           <t>J | 248呎 (1房)
 $653万
 $26,334/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="K8" s="21" t="inlineStr">
@@ -33110,7 +33110,7 @@
           <t>K | 278呎 (1房)
 $546万
 $19,630/呎
-(24年-03月-07日)</t>
+(24年-03月-08日)</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -33118,7 +33118,7 @@
           <t>L | 193呎 (开放式)
 $620万
 $32,118/呎
-(18年-07月-06日)</t>
+(18年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -33133,7 +33133,7 @@
           <t>A | 417呎 (2房)
 $1157万
 $27,755/呎
-(18年-07月-11日)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -33141,7 +33141,7 @@
           <t>B | 251呎 (1房)
 $713万
 $28,398/呎
-(18年-07月-18日)</t>
+(18年-07月-19日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -33149,7 +33149,7 @@
           <t>C | 252呎 (1房)
 $730万
 $28,961/呎
-(18年-07月-26日)</t>
+(18年-07月-27日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -33157,7 +33157,7 @@
           <t>D | 198呎 (开放式)
 $597万
 $30,127/呎
-(21年-10月-06日)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -33165,7 +33165,7 @@
           <t>E | 309呎 (1房)
 $861万
 $27,860/呎
-(21年-12月-16日)</t>
+(21年-12月-17日)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -33173,7 +33173,7 @@
           <t>F | 253呎 (1房)
 $714万
 $28,230/呎
-(18年-07月-12日)</t>
+(18年-07月-13日)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -33181,7 +33181,7 @@
           <t>G | 194呎 (开放式)
 $537万
 $27,701/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -33189,7 +33189,7 @@
           <t>H | 249呎 (1房)
 $653万
 $26,236/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -33197,7 +33197,7 @@
           <t>J | 249呎 (1房)
 $649万
 $26,051/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr">
@@ -33205,7 +33205,7 @@
           <t>K | 278呎 (1房)
 $533万
 $19,186/呎
-(24年-03月-14日)</t>
+(24年-03月-15日)</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -33213,7 +33213,7 @@
           <t>L | 193呎 (开放式)
 $616万
 $31,904/呎
-(18年-07月-23日)</t>
+(18年-07月-24日)</t>
         </is>
       </c>
     </row>
@@ -33228,7 +33228,7 @@
           <t>A | 417呎 (2房)
 $1154万
 $27,679/呎
-(18年-07月-12日)</t>
+(18年-07月-13日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -33236,7 +33236,7 @@
           <t>B | 251呎 (1房)
 $703万
 $28,024/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -33244,7 +33244,7 @@
           <t>C | 252呎 (1房)
 $705万
 $27,995/呎
-(18年-07月-16日)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -33252,7 +33252,7 @@
           <t>D | 198呎 (开放式)
 $595万
 $30,058/呎
-(21年-10月-16日)</t>
+(21年-10月-17日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -33260,7 +33260,7 @@
           <t>E | 309呎 (1房)
 $849万
 $27,491/呎
-(22年-02月-24日)</t>
+(22年-02月-25日)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -33268,7 +33268,7 @@
           <t>F | 253呎 (1房)
 $688万
 $27,193/呎
-(18年-07月-16日)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -33276,7 +33276,7 @@
           <t>G | 194呎 (开放式)
 $534万
 $27,523/呎
-(18年-07月-08日)</t>
+(18年-07月-09日)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -33284,7 +33284,7 @@
           <t>H | 249呎 (1房)
 $642万
 $25,787/呎
-(18年-06月-15日)</t>
+(18年-06月-16日)</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
@@ -33292,7 +33292,7 @@
           <t>J | 249呎 (1房)
 $638万
 $25,604/呎
-(18年-07月-08日)</t>
+(18年-07月-09日)</t>
         </is>
       </c>
       <c r="K10" s="21" t="inlineStr">
@@ -33300,7 +33300,7 @@
           <t>K | 278呎 (1房)
 $530万
 $19,059/呎
-(24年-03月-14日)</t>
+(24年-03月-15日)</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -33308,7 +33308,7 @@
           <t>L | 193呎 (开放式)
 $612万
 $31,695/呎
-(18年-07月-22日)</t>
+(18年-07月-23日)</t>
         </is>
       </c>
     </row>
@@ -33323,7 +33323,7 @@
           <t>A | 417呎 (2房)
 $1161万
 $27,835/呎
-(18年-07月-25日)</t>
+(18年-07月-26日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -33331,7 +33331,7 @@
           <t>B | 251呎 (1房)
 $687万
 $27,357/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -33339,7 +33339,7 @@
           <t>C | 252呎 (1房)
 $711万
 $28,207/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -33347,7 +33347,7 @@
           <t>D | 198呎 (开放式)
 $587万
 $29,653/呎
-(21年-10月-19日)</t>
+(21年-10月-20日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -33355,7 +33355,7 @@
           <t>E | 309呎 (1房)
 $829万
 $26,831/呎
-(22年-05月-11日)</t>
+(22年-05月-12日)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -33363,7 +33363,7 @@
           <t>F | 253呎 (1房)
 $691万
 $27,297/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -33371,7 +33371,7 @@
           <t>G | 194呎 (开放式)
 $525万
 $27,060/呎
-(18年-07月-11日)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -33379,7 +33379,7 @@
           <t>H | 249呎 (1房)
 $638万
 $25,612/呎
-(18年-07月-12日)</t>
+(18年-07月-13日)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -33387,7 +33387,7 @@
           <t>J | 249呎 (1房)
 $633万
 $25,433/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="K11" s="21" t="inlineStr">
@@ -33395,7 +33395,7 @@
           <t>K | 278呎 (1房)
 $526万
 $18,929/呎
-(24年-03月-11日)</t>
+(24年-03月-12日)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -33403,7 +33403,7 @@
           <t>L | 193呎 (开放式)
 $601万
 $31,153/呎
-(18年-07月-26日)</t>
+(18年-07月-27日)</t>
         </is>
       </c>
     </row>
@@ -33418,7 +33418,7 @@
           <t>A | 417呎 (2房)
 $1165万
 $27,934/呎
-(18年-07月-25日)</t>
+(18年-07月-26日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -33426,7 +33426,7 @@
           <t>B | 251呎 (1房)
 $689万
 $27,454/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -33434,7 +33434,7 @@
           <t>C | 252呎 (1房)
 $691万
 $27,437/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -33442,7 +33442,7 @@
           <t>D | 198呎 (开放式)
 $493万
 $24,920/呎
-(23年-06月-04日)</t>
+(23年-06月-05日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -33450,7 +33450,7 @@
           <t>E | 309呎 (1房)
 $725万
 $23,464/呎
-(22年-12月-21日)</t>
+(22年-12月-22日)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -33458,7 +33458,7 @@
           <t>F | 253呎 (1房)
 $679万
 $26,837/呎
-(18年-06月-22日)</t>
+(18年-06月-23日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -33466,7 +33466,7 @@
           <t>G | 194呎 (开放式)
 $521万
 $26,879/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -33474,7 +33474,7 @@
           <t>H | 249呎 (1房)
 $653万
 $26,244/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
@@ -33482,7 +33482,7 @@
           <t>J | 249呎 (1房)
 $629万
 $25,257/呎
-(18年-07月-12日)</t>
+(18年-07月-13日)</t>
         </is>
       </c>
       <c r="K12" s="21" t="inlineStr">
@@ -33490,7 +33490,7 @@
           <t>K | 278呎 (1房)
 $617万
 $22,193/呎
-(23年-09月-13日)</t>
+(23年-09月-14日)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -33498,7 +33498,7 @@
           <t>L | 193呎 (开放式)
 $597万
 $30,946/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
     </row>
@@ -33513,7 +33513,7 @@
           <t>A | 417呎 (2房)
 $1123万
 $26,935/呎
-(18年-07月-12日)</t>
+(18年-07月-13日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -33521,7 +33521,7 @@
           <t>B | 251呎 (1房)
 $684万
 $27,270/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -33529,7 +33529,7 @@
           <t>C | 252呎 (1房)
 $687万
 $27,252/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -33537,7 +33537,7 @@
           <t>D | 198呎 (开放式)
 $611万
 $30,861/呎
-(18年-10月-22日)</t>
+(18年-10月-23日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -33545,7 +33545,7 @@
           <t>E | 309呎 (1房)
 $818万
 $26,467/呎
-(21年-10月-06日)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -33553,7 +33553,7 @@
           <t>F | 253呎 (1房)
 $682万
 $26,941/呎
-(18年-07月-12日)</t>
+(18年-07月-13日)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -33561,7 +33561,7 @@
           <t>G | 194呎 (开放式)
 $518万
 $26,698/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -33569,7 +33569,7 @@
           <t>H | 249呎 (1房)
 $629万
 $25,268/呎
-(18年-07月-02日)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -33577,7 +33577,7 @@
           <t>J | 249呎 (1房)
 $631万
 $25,349/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr">
@@ -33585,7 +33585,7 @@
           <t>K | 278呎 (1房)
 $613万
 $22,043/呎
-(23年-08月-30日)</t>
+(23年-08月-31日)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -33593,7 +33593,7 @@
           <t>L | 193呎 (开放式)
 $576万
 $29,839/呎
-(18年-07月-12日)</t>
+(18年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -33608,7 +33608,7 @@
           <t>A | 417呎 (2房)
 $1116万
 $26,751/呎
-(18年-07月-18日)</t>
+(18年-07月-19日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -33616,7 +33616,7 @@
           <t>B | 251呎 (1房)
 $694万
 $27,643/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -33624,7 +33624,7 @@
           <t>C | 252呎 (1房)
 $689万
 $27,352/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -33632,7 +33632,7 @@
           <t>D | 198呎 (开放式)
 $607万
 $30,642/呎
-(19年-08月-15日)</t>
+(19年-08月-16日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -33640,7 +33640,7 @@
           <t>E | 309呎 (1房)
 $866万
 $28,042/呎
-(18年-09月-05日)</t>
+(18年-09月-06日)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -33648,7 +33648,7 @@
           <t>F | 253呎 (1房)
 $677万
 $26,762/呎
-(18年-07月-16日)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -33656,7 +33656,7 @@
           <t>G | 194呎 (开放式)
 $515万
 $26,522/呎
-(18年-06月-15日)</t>
+(18年-06月-16日)</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -33664,7 +33664,7 @@
           <t>H | 249呎 (1房)
 $631万
 $25,357/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
@@ -33672,7 +33672,7 @@
           <t>J | 249呎 (1房)
 $620万
 $24,910/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="K14" s="21" t="inlineStr">
@@ -33680,7 +33680,7 @@
           <t>K | 278呎 (1房)
 $600万
 $21,588/呎
-(23年-11月-13日)</t>
+(23年-11月-14日)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -33688,7 +33688,7 @@
           <t>L | 193呎 (开放式)
 $589万
 $30,518/呎
-(18年-07月-30日)</t>
+(18年-07月-31日)</t>
         </is>
       </c>
     </row>
@@ -33703,7 +33703,7 @@
           <t>A | 417呎 (2房)
 $1108万
 $26,565/呎
-(18年-07月-18日)</t>
+(18年-07月-19日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -33711,7 +33711,7 @@
           <t>B | 251呎 (1房)
 $675万
 $26,891/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -33719,7 +33719,7 @@
           <t>C | 252呎 (1房)
 $692万
 $27,449/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -33727,7 +33727,7 @@
           <t>D | 198呎 (开放式)
 $427万
 $21,554/呎
-(23年-10月-29日)</t>
+(23年-10月-30日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -33735,7 +33735,7 @@
           <t>E | 309呎 (1房)
 $835万
 $27,038/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -33743,7 +33743,7 @@
           <t>F | 253呎 (1房)
 $687万
 $27,142/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -33751,7 +33751,7 @@
           <t>G | 194呎 (开放式)
 $516万
 $26,618/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -33759,7 +33759,7 @@
           <t>H | 249呎 (1房)
 $1751万
 $70,317/呎
-(18年-06月-15日)</t>
+(18年-06月-16日)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -33767,7 +33767,7 @@
           <t>J | 249呎 (1房)
 $622万
 $24,999/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -33775,7 +33775,7 @@
           <t>K | 278呎 (1房)
 $663万
 $23,856/呎
-(23年-07月-30日)</t>
+(23年-07月-31日)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -33783,7 +33783,7 @@
           <t>L | 193呎 (开放式)
 $586万
 $30,355/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
     </row>
@@ -33798,7 +33798,7 @@
           <t>A | 417呎 (2房)
 $1100万
 $26,380/呎
-(18年-07月-15日)</t>
+(18年-07月-16日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -33806,7 +33806,7 @@
           <t>B | 251呎 (1房)
 $670万
 $26,708/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -33814,7 +33814,7 @@
           <t>C | 252呎 (1房)
 $680万
 $26,979/呎
-(18年-07月-11日)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -33822,7 +33822,7 @@
           <t>D | 198呎 (开放式)
 $455万
 $22,980/呎
-(23年-08月-30日)</t>
+(23年-08月-31日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -33830,7 +33830,7 @@
           <t>E | 311呎 (1房)
 $821万
 $26,398/呎
-(18年-06月-22日)</t>
+(18年-06月-23日)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -33838,7 +33838,7 @@
           <t>F | 253呎 (1房)
 $661万
 $26,131/呎
-(18年-07月-12日)</t>
+(18年-07月-13日)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -33846,7 +33846,7 @@
           <t>G | 194呎 (开放式)
 $508万
 $26,184/呎
-(18年-07月-11日)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -33854,7 +33854,7 @@
           <t>H | 249呎 (1房)
 $636万
 $25,527/呎
-(18年-07月-09日)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
@@ -33862,7 +33862,7 @@
           <t>J | 249呎 (1房)
 $612万
 $24,563/呎
-(18年-06月-15日)</t>
+(18年-06月-16日)</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
@@ -33870,7 +33870,7 @@
           <t>K | 278呎 (1房)
 $642万
 $23,094/呎
-(23年-04月-10日)</t>
+(23年-04月-11日)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -33878,7 +33878,7 @@
           <t>L | 193呎 (开放式)
 $570万
 $29,531/呎
-(18年-07月-12日)</t>
+(18年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -33893,7 +33893,7 @@
           <t>A | 417呎 (2房)
 $1092万
 $26,196/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -33901,7 +33901,7 @@
           <t>B | 251呎 (1房)
 $666万
 $26,517/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -33909,7 +33909,7 @@
           <t>C | 252呎 (1房)
 $675万
 $26,796/呎
-(18年-07月-09日)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -33917,7 +33917,7 @@
           <t>D | 198呎 (开放式)
 $588万
 $29,690/呎
-(18年-08月-27日)</t>
+(18年-08月-28日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -33925,7 +33925,7 @@
           <t>E | 311呎 (1房)
 $815万
 $26,218/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -33933,7 +33933,7 @@
           <t>F | 253呎 (1房)
 $677万
 $26,778/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -33941,7 +33941,7 @@
           <t>G | 194呎 (开放式)
 $504万
 $25,993/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -33949,7 +33949,7 @@
           <t>H | 249呎 (1房)
 $631万
 $25,346/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -33957,7 +33957,7 @@
           <t>J | 249呎 (1房)
 $614万
 $24,648/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="K17" s="21" t="inlineStr">
@@ -33965,7 +33965,7 @@
           <t>K | 278呎 (1房)
 $638万
 $22,934/呎
-(23年-04月-13日)</t>
+(23年-04月-14日)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -33973,7 +33973,7 @@
           <t>L | 193呎 (开放式)
 $566万
 $29,327/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
     </row>
@@ -33988,7 +33988,7 @@
           <t>A | 417呎 (2房)
 $1085万
 $26,010/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -33996,7 +33996,7 @@
           <t>B | 251呎 (1房)
 $663万
 $26,425/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -34004,7 +34004,7 @@
           <t>C | 252呎 (1房)
 $673万
 $26,697/呎
-(18年-07月-09日)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -34012,7 +34012,7 @@
           <t>D | 197呎 (开放式)
 $586万
 $29,739/呎
-(18年-08月-23日)</t>
+(18年-08月-24日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -34020,7 +34020,7 @@
           <t>E | 309呎 (1房)
 $818万
 $26,476/呎
-(18年-07月-08日)</t>
+(18年-07月-09日)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -34028,7 +34028,7 @@
           <t>F | 253呎 (1房)
 $661万
 $26,140/呎
-(18年-07月-16日)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -34036,7 +34036,7 @@
           <t>G | 194呎 (开放式)
 $502万
 $25,900/呎
-(18年-07月-08日)</t>
+(18年-07月-09日)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -34044,7 +34044,7 @@
           <t>H | 249呎 (1房)
 $616万
 $24,744/呎
-(18年-07月-12日)</t>
+(18年-07月-13日)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
@@ -34052,7 +34052,7 @@
           <t>J | 249呎 (1房)
 $605万
 $24,303/呎
-(18年-07月-08日)</t>
+(18年-07月-09日)</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -34060,7 +34060,7 @@
           <t>K | 278呎 (1房)
 $635万
 $22,853/呎
-(23年-08月-01日)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -34068,7 +34068,7 @@
           <t>L | 193呎 (开放式)
 $562万
 $29,118/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
     </row>
@@ -34083,7 +34083,7 @@
           <t>A | 417呎 (2房)
 $1069万
 $25,639/呎
-(18年-07月-12日)</t>
+(18年-07月-13日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -34091,7 +34091,7 @@
           <t>B | 251呎 (1房)
 $658万
 $26,234/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -34099,7 +34099,7 @@
           <t>C | 252呎 (1房)
 $668万
 $26,507/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -34107,7 +34107,7 @@
           <t>D | 198呎 (开放式)
 $447万
 $22,574/呎
-(23年-09月-27日)</t>
+(23年-09月-28日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -34115,7 +34115,7 @@
           <t>E | 311呎 (1房)
 $806万
 $25,929/呎
-(18年-07月-12日)</t>
+(18年-07月-13日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -34123,7 +34123,7 @@
           <t>F | 253呎 (1房)
 $657万
 $25,966/呎
-(18年-07月-11日)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -34131,7 +34131,7 @@
           <t>G | 194呎 (开放式)
 $504万
 $25,989/呎
-(18年-07月-09日)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -34139,7 +34139,7 @@
           <t>H | 249呎 (1房)
 $612万
 $24,567/呎
-(18年-07月-11日)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">
@@ -34147,7 +34147,7 @@
           <t>J | 248呎 (1房)
 $620万
 $24,994/呎
-(18年-07月-11日)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
@@ -34155,7 +34155,7 @@
           <t>K | 278呎 (1房)
 $639万
 $22,987/呎
-(23年-05月-14日)</t>
+(23年-05月-15日)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -34163,7 +34163,7 @@
           <t>L | 193呎 (开放式)
 $544万
 $28,205/呎
-(18年-06月-22日)</t>
+(18年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -34178,7 +34178,7 @@
           <t>A | 417呎 (2房)
 $1663万
 $39,889/呎
-(18年-07月-09日)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -34186,7 +34186,7 @@
           <t>B | 251呎 (1房)
 $654万
 $26,046/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -34194,7 +34194,7 @@
           <t>C | 252呎 (1房)
 $656万
 $26,050/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -34202,7 +34202,7 @@
           <t>D | 198呎 (开放式)
 $438万
 $22,102/呎
-(23年-09月-03日)</t>
+(23年-09月-04日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -34210,7 +34210,7 @@
           <t>E | 311呎 (1房)
 $795万
 $25,559/呎
-(18年-07月-09日)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -34218,7 +34218,7 @@
           <t>F | 253呎 (1房)
 $680万
 $26,858/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -34226,7 +34226,7 @@
           <t>G | 194呎 (开放式)
 $495万
 $25,537/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -34234,7 +34234,7 @@
           <t>H | 249呎 (1房)
 $607万
 $24,393/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -34242,7 +34242,7 @@
           <t>J | 249呎 (1房)
 $596万
 $23,952/呎
-(18年-07月-02日)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
@@ -34250,7 +34250,7 @@
           <t>K | 278呎 (1房)
 $626万
 $22,532/呎
-(23年-05月-03日)</t>
+(23年-05月-04日)</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -34258,7 +34258,7 @@
           <t>L | 193呎 (开放式)
 $538万
 $27,885/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
     </row>
@@ -34273,7 +34273,7 @@
           <t>A | 417呎 (2房)
 $1035万
 $24,823/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -34281,7 +34281,7 @@
           <t>B | 251呎 (1房)
 $649万
 $25,863/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -34289,7 +34289,7 @@
           <t>C | 252呎 (1房)
 $665万
 $26,406/呎
-(18年-07月-16日)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -34297,7 +34297,7 @@
           <t>D | 198呎 (开放式)
 $573万
 $28,956/呎
-(18年-09月-03日)</t>
+(18年-09月-04日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -34305,7 +34305,7 @@
           <t>E | 311呎 (1房)
 $789万
 $25,371/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -34313,7 +34313,7 @@
           <t>F | 253呎 (1房)
 $648万
 $25,609/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -34321,7 +34321,7 @@
           <t>G | 194呎 (开放式)
 $492万
 $25,361/呎
-(18年-06月-15日)</t>
+(18年-06月-16日)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -34329,7 +34329,7 @@
           <t>H | 249呎 (1房)
 $645万
 $25,890/呎
-(21年-06月-02日)</t>
+(21年-06月-03日)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -34337,7 +34337,7 @@
           <t>J | 249呎 (1房)
 $598万
 $24,031/呎
-(18年-07月-09日)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="K21" s="21" t="inlineStr">
@@ -34345,7 +34345,7 @@
           <t>K | 278呎 (1房)
 $630万
 $22,659/呎
-(23年-04月-11日)</t>
+(23年-04月-12日)</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -34353,7 +34353,7 @@
           <t>L | 193呎 (开放式)
 $534万
 $27,681/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
     </row>
@@ -34368,7 +34368,7 @@
           <t>A | 417呎 (2房)
 $1028万
 $24,641/呎
-(18年-07月-08日)</t>
+(18年-07月-09日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -34376,7 +34376,7 @@
           <t>B | 251呎 (1房)
 $644万
 $25,671/呎
-(18年-07月-02日)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -34384,7 +34384,7 @@
           <t>C | 252呎 (1房)
 $654万
 $25,947/呎
-(18年-07月-02日)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -34392,7 +34392,7 @@
           <t>D | 197呎 (开放式)
 $575万
 $29,195/呎
-(18年-08月-21日)</t>
+(18年-08月-22日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -34400,7 +34400,7 @@
           <t>E | 311呎 (1房)
 $783万
 $25,185/呎
-(18年-07月-02日)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -34408,7 +34408,7 @@
           <t>F | 253呎 (1房)
 $637万
 $25,166/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -34416,7 +34416,7 @@
           <t>G | 194呎 (开放式)
 $489万
 $25,185/呎
-(18年-07月-09日)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -34424,7 +34424,7 @@
           <t>H | 249呎 (1房)
 $592万
 $23,792/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -34432,7 +34432,7 @@
           <t>J | 248呎 (1房)
 $588万
 $23,704/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="K22" s="21" t="inlineStr">
@@ -34440,7 +34440,7 @@
           <t>K | 278呎 (1房)
 $726万
 $26,100/呎
-(18年-07月-16日)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
@@ -34448,7 +34448,7 @@
           <t>L | 193呎 (开放式)
 $525万
 $27,186/呎
-(18年-07月-16日)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -34463,7 +34463,7 @@
           <t>A | 417呎 (2房)
 $1031万
 $24,714/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -34471,7 +34471,7 @@
           <t>B | 251呎 (1房)
 $652万
 $25,975/呎
-(19年-07月-09日)</t>
+(19年-07月-10日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -34479,7 +34479,7 @@
           <t>C | 252呎 (1房)
 $663万
 $26,301/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -34487,7 +34487,7 @@
           <t>D | 198呎 (开放式)
 $533万
 $26,897/呎
-(18年-07月-15日)</t>
+(18年-07月-16日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -34495,7 +34495,7 @@
           <t>E | 309呎 (1房)
 $769万
 $24,900/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -34503,7 +34503,7 @@
           <t>F | 253呎 (1房)
 $639万
 $25,252/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -34511,7 +34511,7 @@
           <t>G | 194呎 (开放式)
 $511万
 $26,325/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -34519,7 +34519,7 @@
           <t>H | 249呎 (1房)
 $594万
 $23,869/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -34527,7 +34527,7 @@
           <t>J | 249呎 (1房)
 $584万
 $23,437/呎
-(18年-07月-12日)</t>
+(18年-07月-13日)</t>
         </is>
       </c>
       <c r="K23" s="21" t="inlineStr">
@@ -34535,7 +34535,7 @@
           <t>K | 278呎 (1房)
 $720万
 $25,913/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="L23" s="21" t="inlineStr">
@@ -34543,7 +34543,7 @@
           <t>L | 193呎 (开放式)
 $521万
 $26,984/呎
-(18年-07月-16日)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -34558,7 +34558,7 @@
           <t>A | 417呎 (2房)
 $1023万
 $24,529/呎
-(18年-07月-18日)</t>
+(18年-07月-19日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -34566,7 +34566,7 @@
           <t>B | 251呎 (1房)
 $635万
 $25,297/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -34574,7 +34574,7 @@
           <t>C | 252呎 (1房)
 $644万
 $25,573/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -34582,7 +34582,7 @@
           <t>D | 198呎 (开放式)
 $529万
 $26,701/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -34590,7 +34590,7 @@
           <t>E | 309呎 (1房)
 $772万
 $24,972/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -34598,7 +34598,7 @@
           <t>F | 253呎 (1房)
 $641万
 $25,335/呎
-(18年-07月-16日)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -34606,7 +34606,7 @@
           <t>G | 194呎 (开放式)
 $492万
 $25,350/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -34614,7 +34614,7 @@
           <t>H | 249呎 (1房)
 $590万
 $23,692/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -34622,7 +34622,7 @@
           <t>J | 249呎 (1房)
 $579万
 $23,258/呎
-(18年-06月-15日)</t>
+(18年-06月-16日)</t>
         </is>
       </c>
       <c r="K24" s="21" t="inlineStr">
@@ -34630,7 +34630,7 @@
           <t>K | 278呎 (1房)
 $708万
 $25,455/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="L24" s="21" t="inlineStr">
@@ -34638,7 +34638,7 @@
           <t>L | 193呎 (开放式)
 $517万
 $26,777/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
     </row>
@@ -34653,7 +34653,7 @@
           <t>A | 417呎 (2房)
 $1008万
 $24,183/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -34661,7 +34661,7 @@
           <t>B | 251呎 (1房)
 $646万
 $25,726/呎
-(18年-06月-15日)</t>
+(18年-06月-16日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -34669,7 +34669,7 @@
           <t>C | 252呎 (1房)
 $635万
 $25,216/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -34677,7 +34677,7 @@
           <t>D | 197呎 (开放式)
 $532万
 $27,016/呎
-(18年-07月-11日)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -34685,7 +34685,7 @@
           <t>E | 309呎 (1房)
 $785万
 $25,401/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -34693,7 +34693,7 @@
           <t>F | 253呎 (1房)
 $632万
 $24,987/呎
-(18年-07月-11日)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -34701,7 +34701,7 @@
           <t>G | 194呎 (开放式)
 $485万
 $25,000/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -34709,7 +34709,7 @@
           <t>H | 249呎 (1房)
 $582万
 $23,361/呎
-(18年-06月-15日)</t>
+(18年-06月-16日)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">
@@ -34717,7 +34717,7 @@
           <t>J | 248呎 (1房)
 $583万
 $23,512/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="K25" s="21" t="inlineStr">
@@ -34725,7 +34725,7 @@
           <t>K | 278呎 (1房)
 $713万
 $25,630/呎
-(18年-07月-15日)</t>
+(18年-07月-16日)</t>
         </is>
       </c>
       <c r="L25" s="21" t="inlineStr">
@@ -34733,7 +34733,7 @@
           <t>L | 193呎 (开放式)
 $515万
 $26,674/呎
-(18年-07月-11日)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
     </row>
@@ -34748,7 +34748,7 @@
           <t>A | 417呎 (2房)
 $762万
 $18,264/呎
-(24年-03月-26日)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -34756,7 +34756,7 @@
           <t>B | 251呎 (1房)
 $628万
 $25,014/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -34764,7 +34764,7 @@
           <t>C | 252呎 (1房)
 $637万
 $25,291/呎
-(18年-06月-15日)</t>
+(18年-06月-16日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -34772,7 +34772,7 @@
           <t>D | 198呎 (开放式)
 $528万
 $26,681/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -34780,7 +34780,7 @@
           <t>E | 311呎 (1房)
 $763万
 $24,534/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -34788,7 +34788,7 @@
           <t>F | 253呎 (1房)
 $621万
 $24,546/呎
-(18年-06月-22日)</t>
+(18年-06月-23日)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -34796,7 +34796,7 @@
           <t>G | 194呎 (开放式)
 $482万
 $24,821/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -34804,7 +34804,7 @@
           <t>H | 248呎 (1房)
 $583万
 $23,524/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
@@ -34812,7 +34812,7 @@
           <t>J | 249呎 (1房)
 $573万
 $23,002/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="K26" s="21" t="inlineStr">
@@ -34820,7 +34820,7 @@
           <t>K | 278呎 (1房)
 $707万
 $25,440/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="L26" s="21" t="inlineStr">
@@ -34828,7 +34828,7 @@
           <t>L | 193呎 (开放式)
 $553万
 $28,661/呎
-(18年-07月-23日)</t>
+(18年-07月-24日)</t>
         </is>
       </c>
     </row>
@@ -34843,7 +34843,7 @@
           <t>A | 417呎 (2房)
 $1129万
 $27,085/呎
-(18年-09月-11日)</t>
+(18年-09月-12日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -34851,7 +34851,7 @@
           <t>B | 251呎 (1房)
 $621万
 $24,734/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -34859,7 +34859,7 @@
           <t>C | 252呎 (1房)
 $630万
 $25,013/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -34867,7 +34867,7 @@
           <t>D | 198呎 (开放式)
 $522万
 $26,376/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -34875,7 +34875,7 @@
           <t>E | 309呎 (1房)
 $754万
 $24,410/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -34883,7 +34883,7 @@
           <t>F | 253呎 (1房)
 $621万
 $24,539/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -34891,7 +34891,7 @@
           <t>G | 194呎 (开放式)
 $476万
 $24,544/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -34899,7 +34899,7 @@
           <t>H | 249呎 (1房)
 $645万
 $25,897/呎
-(18年-07月-11日)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -34907,7 +34907,7 @@
           <t>J | 249呎 (1房)
 $566万
 $22,739/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="K27" s="21" t="inlineStr">
@@ -34915,7 +34915,7 @@
           <t>K | 278呎 (1房)
 $699万
 $25,157/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -34923,7 +34923,7 @@
           <t>L | 193呎 (开放式)
 $499万
 $25,847/呎
-(18年-07月-09日)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
     </row>
@@ -34938,7 +34938,7 @@
           <t>A | 379呎 (2房)
 $788万
 $20,792/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -34946,7 +34946,7 @@
           <t>B | 229呎 (1房)
 $721万
 $31,480/呎
-(21年-05月-26日)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -34954,7 +34954,7 @@
           <t>C | 230呎 (1房)
 $740万
 $32,167/呎
-(22年-01月-17日)</t>
+(22年-01月-18日)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -34962,7 +34962,7 @@
           <t>D | 175呎 (开放式)
 $480万
 $27,429/呎
-(24年-04月-18日)</t>
+(24年-04月-19日)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -34970,7 +34970,7 @@
           <t>E | 290呎 (1房)
 $680万
 $23,448/呎
-(26年-01月-11日)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -34978,7 +34978,7 @@
           <t>F | 233呎 (1房)
 $610万
 $26,180/呎
-(23年-07月-02日)</t>
+(23年-07月-03日)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -34986,7 +34986,7 @@
           <t>G | 171呎 (开放式)
 $596万
 $34,837/呎
-(22年-09月-22日)</t>
+(22年-09月-23日)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -34994,7 +34994,7 @@
           <t>H | 227呎 (1房)
 $681万
 $30,005/呎
-(21年-06月-08日)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">
@@ -35002,7 +35002,7 @@
           <t>J | 227呎 (1房)
 $693万
 $30,511/呎
-(21年-09月-19日)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
@@ -35010,7 +35010,7 @@
           <t>K | 257呎 (1房)
 $635万
 $24,708/呎
-(26年-03月-09日)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr">
@@ -35018,7 +35018,7 @@
           <t>L | 171呎 (开放式)
 $618万
 $36,123/呎
-(22年-07月-13日)</t>
+(22年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -35198,7 +35198,7 @@
           <t>A | 632呎 (3房)
 $2000万
 $31,646/呎
-(24年-04月-04日)</t>
+(24年-04月-05日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -35206,7 +35206,7 @@
           <t>B | 506呎 (3房)
 $1689万
 $33,375/呎
-(21年-08月-01日)</t>
+(21年-08月-02日)</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -35222,7 +35222,7 @@
           <t>D | 579呎 (3房)
 $1660万
 $28,670/呎
-(22年-10月-30日)</t>
+(22年-10月-31日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr"/>
@@ -35244,7 +35244,7 @@
           <t>A | 417呎 (2房)
 $951万
 $22,803/呎
-(23年-12月-06日)</t>
+(23年-12月-07日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -35252,7 +35252,7 @@
           <t>B | 251呎 (1房)
 $740万
 $29,496/呎
-(18年-07月-18日)</t>
+(18年-07月-19日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -35260,7 +35260,7 @@
           <t>C | 252呎 (1房)
 $739万
 $29,341/呎
-(18年-07月-11日)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -35268,7 +35268,7 @@
           <t>D | 198呎 (开放式)
 $637万
 $32,160/呎
-(18年-09月-05日)</t>
+(18年-09月-06日)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -35276,7 +35276,7 @@
           <t>E | 307呎 (1房)
 $766万
 $24,964/呎
-(23年-04月-10日)</t>
+(23年-04月-11日)</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -35284,7 +35284,7 @@
           <t>F | 253呎 (1房)
 $702万
 $27,747/呎
-(21年-11月-15日)</t>
+(21年-11月-16日)</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -35292,7 +35292,7 @@
           <t>G | 194呎 (开放式)
 $550万
 $28,336/呎
-(21年-11月-29日)</t>
+(21年-11月-30日)</t>
         </is>
       </c>
       <c r="I6" s="21" t="inlineStr">
@@ -35300,7 +35300,7 @@
           <t>H | 249呎 (1房)
 $708万
 $28,449/呎
-(21年-12月-20日)</t>
+(21年-12月-21日)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
@@ -35308,7 +35308,7 @@
           <t>J | 249呎 (1房)
 $751万
 $30,144/呎
-(18年-09月-27日)</t>
+(18年-09月-28日)</t>
         </is>
       </c>
       <c r="K6" s="21" t="inlineStr">
@@ -35316,7 +35316,7 @@
           <t>K | 278呎 (1房)
 $776万
 $27,926/呎
-(22年-04月-25日)</t>
+(22年-04月-26日)</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
@@ -35324,7 +35324,7 @@
           <t>L | 193呎 (开放式)
 $383万
 $19,835/呎
-(25年-08月-27日)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -35339,7 +35339,7 @@
           <t>A | 417呎 (2房)
 $1233万
 $29,575/呎
-(19年-05月-22日)</t>
+(19年-05月-23日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -35347,7 +35347,7 @@
           <t>B | 251呎 (1房)
 $724万
 $28,829/呎
-(18年-07月-12日)</t>
+(18年-07月-13日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -35355,7 +35355,7 @@
           <t>C | 252呎 (1房)
 $738万
 $29,291/呎
-(18年-07月-12日)</t>
+(18年-07月-13日)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -35363,7 +35363,7 @@
           <t>D | 198呎 (开放式)
 $629万
 $31,758/呎
-(18年-08月-16日)</t>
+(18年-08月-17日)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -35371,7 +35371,7 @@
           <t>E | 307呎 (1房)
 $885万
 $28,815/呎
-(21年-09月-02日)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -35379,7 +35379,7 @@
           <t>F | 253呎 (1房)
 $701万
 $27,714/呎
-(21年-11月-03日)</t>
+(21年-11月-04日)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -35387,7 +35387,7 @@
           <t>G | 194呎 (开放式)
 $543万
 $27,993/呎
-(21年-12月-01日)</t>
+(21年-12月-02日)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -35395,7 +35395,7 @@
           <t>H | 249呎 (1房)
 $707万
 $28,411/呎
-(21年-11月-10日)</t>
+(21年-11月-11日)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -35403,7 +35403,7 @@
           <t>J | 249呎 (1房)
 $726万
 $29,162/呎
-(18年-09月-13日)</t>
+(18年-09月-14日)</t>
         </is>
       </c>
       <c r="K7" s="21" t="inlineStr">
@@ -35411,7 +35411,7 @@
           <t>K | 278呎 (1房)
 $767万
 $27,573/呎
-(22年-03月-01日)</t>
+(22年-03月-02日)</t>
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -35419,7 +35419,7 @@
           <t>L | 193呎 (开放式)
 $425万
 $22,002/呎
-(24年-04月-11日)</t>
+(24年-04月-12日)</t>
         </is>
       </c>
     </row>
@@ -35434,7 +35434,7 @@
           <t>A | 417呎 (2房)
 $1127万
 $27,034/呎
-(18年-07月-18日)</t>
+(18年-07月-19日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -35442,7 +35442,7 @@
           <t>B | 251呎 (1房)
 $695万
 $27,679/呎
-(18年-07月-24日)</t>
+(18年-07月-25日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -35450,7 +35450,7 @@
           <t>C | 252呎 (1房)
 $709万
 $28,133/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -35458,7 +35458,7 @@
           <t>D | 198呎 (开放式)
 $597万
 $30,141/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -35466,7 +35466,7 @@
           <t>E | 307呎 (1房)
 $848万
 $27,633/呎
-(21年-10月-21日)</t>
+(21年-10月-22日)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -35474,7 +35474,7 @@
           <t>F | 253呎 (1房)
 $647万
 $25,556/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -35482,7 +35482,7 @@
           <t>G | 194呎 (开放式)
 $517万
 $26,637/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr">
@@ -35490,7 +35490,7 @@
           <t>H | 249呎 (1房)
 $618万
 $24,817/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
@@ -35498,7 +35498,7 @@
           <t>J | 249呎 (1房)
 $647万
 $26,003/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="K8" s="21" t="inlineStr">
@@ -35506,7 +35506,7 @@
           <t>K | 278呎 (1房)
 $784万
 $28,203/呎
-(18年-08月-15日)</t>
+(18年-08月-16日)</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -35514,7 +35514,7 @@
           <t>L | 193呎 (开放式)
 $527万
 $27,319/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
     </row>
@@ -35529,7 +35529,7 @@
           <t>A | 417呎 (2房)
 $1134万
 $27,199/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -35537,7 +35537,7 @@
           <t>B | 251呎 (1房)
 $660万
 $26,298/呎
-(18年-06月-24日)</t>
+(18年-06月-25日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -35545,7 +35545,7 @@
           <t>C | 252呎 (1房)
 $660万
 $26,179/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -35553,7 +35553,7 @@
           <t>D | 198呎 (开放式)
 $589万
 $29,738/呎
-(18年-06月-30日)</t>
+(18年-07月-01日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -35561,7 +35561,7 @@
           <t>E | 307呎 (1房)
 $884万
 $28,782/呎
-(19年-06月-19日)</t>
+(19年-06月-20日)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -35569,7 +35569,7 @@
           <t>F | 253呎 (1房)
 $642万
 $25,395/呎
-(18年-06月-25日)</t>
+(18年-06月-26日)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -35577,7 +35577,7 @@
           <t>G | 194呎 (开放式)
 $498万
 $25,655/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -35585,7 +35585,7 @@
           <t>H | 249呎 (1房)
 $614万
 $24,655/呎
-(18年-06月-08日)</t>
+(18年-06月-09日)</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -35593,7 +35593,7 @@
           <t>J | 249呎 (1房)
 $630万
 $25,307/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr">
@@ -35601,7 +35601,7 @@
           <t>K | 278呎 (1房)
 $643万
 $23,131/呎
-(23年-03月-08日)</t>
+(23年-03月-09日)</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -35609,7 +35609,7 @@
           <t>L | 193呎 (开放式)
 $524万
 $27,141/呎
-(18年-06月-08日)</t>
+(18年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -35624,7 +35624,7 @@
           <t>A | 417呎 (2房)
 $1098万
 $26,334/呎
-(18年-07月-09日)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -35632,7 +35632,7 @@
           <t>B | 251呎 (1房)
 $645万
 $25,687/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -35640,7 +35640,7 @@
           <t>C | 252呎 (1房)
 $644万
 $25,575/呎
-(18年-06月-08日)</t>
+(18年-06月-09日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -35648,7 +35648,7 @@
           <t>D | 198呎 (开放式)
 $553万
 $27,947/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -35656,7 +35656,7 @@
           <t>E | 307呎 (1房)
 $881万
 $28,700/呎
-(18年-08月-21日)</t>
+(18年-08月-22日)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -35664,7 +35664,7 @@
           <t>F | 253呎 (1房)
 $645万
 $25,495/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -35672,7 +35672,7 @@
           <t>G | 194呎 (开放式)
 $500万
 $25,762/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -35680,7 +35680,7 @@
           <t>H | 249呎 (1房)
 $610万
 $24,493/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
@@ -35688,7 +35688,7 @@
           <t>J | 248呎 (1房)
 $619万
 $24,972/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="K10" s="21" t="inlineStr">
@@ -35696,7 +35696,7 @@
           <t>K | 278呎 (1房)
 $766万
 $27,543/呎
-(18年-08月-14日)</t>
+(18年-08月-15日)</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -35704,7 +35704,7 @@
           <t>L | 193呎 (开放式)
 $526万
 $27,248/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -35719,7 +35719,7 @@
           <t>A | 417呎 (2房)
 $1072万
 $25,716/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -35727,7 +35727,7 @@
           <t>B | 251呎 (1房)
 $650万
 $25,878/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -35735,7 +35735,7 @@
           <t>C | 252呎 (1房)
 $643万
 $25,505/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -35743,7 +35743,7 @@
           <t>D | 198呎 (开放式)
 $546万
 $27,568/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -35751,7 +35751,7 @@
           <t>E | 308呎 (1房)
 $869万
 $28,217/呎
-(18年-08月-13日)</t>
+(18年-08月-14日)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -35759,7 +35759,7 @@
           <t>F | 253呎 (1房)
 $634万
 $25,068/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -35767,7 +35767,7 @@
           <t>G | 194呎 (开放式)
 $491万
 $25,327/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -35775,7 +35775,7 @@
           <t>H | 249呎 (1房)
 $600万
 $24,078/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -35783,7 +35783,7 @@
           <t>J | 249呎 (1房)
 $615万
 $24,708/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="K11" s="21" t="inlineStr">
@@ -35791,7 +35791,7 @@
           <t>K | 278呎 (1房)
 $761万
 $27,362/呎
-(18年-07月-26日)</t>
+(18年-07月-27日)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -35799,7 +35799,7 @@
           <t>L | 193呎 (开放式)
 $517万
 $26,792/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
     </row>
@@ -35814,7 +35814,7 @@
           <t>A | 417呎 (2房)
 $1065万
 $25,541/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -35822,7 +35822,7 @@
           <t>B | 251呎 (1房)
 $625万
 $24,920/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -35830,7 +35830,7 @@
           <t>C | 252呎 (1房)
 $632万
 $25,073/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -35838,7 +35838,7 @@
           <t>D | 197呎 (开放式)
 $542万
 $27,518/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -35846,7 +35846,7 @@
           <t>E | 308呎 (1房)
 $881万
 $28,608/呎
-(18年-07月-16日)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -35854,7 +35854,7 @@
           <t>F | 253呎 (1房)
 $637万
 $25,169/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -35862,7 +35862,7 @@
           <t>G | 194呎 (开放式)
 $488万
 $25,160/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -35870,7 +35870,7 @@
           <t>H | 249呎 (1房)
 $596万
 $23,918/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
@@ -35878,7 +35878,7 @@
           <t>J | 249呎 (1房)
 $618万
 $24,802/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="K12" s="21" t="inlineStr">
@@ -35886,7 +35886,7 @@
           <t>K | 278呎 (1房)
 $727万
 $26,151/呎
-(18年-07月-08日)</t>
+(18年-07月-09日)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -35894,7 +35894,7 @@
           <t>L | 193呎 (开放式)
 $514万
 $26,615/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
     </row>
@@ -35909,7 +35909,7 @@
           <t>A | 417呎 (2房)
 $1069万
 $25,635/呎
-(18年-07月-18日)</t>
+(18年-07月-19日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -35917,7 +35917,7 @@
           <t>B | 251呎 (1房)
 $621万
 $24,749/呎
-(18年-07月-08日)</t>
+(18年-07月-09日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -35925,7 +35925,7 @@
           <t>C | 252呎 (1房)
 $628万
 $24,907/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -35933,7 +35933,7 @@
           <t>D | 198呎 (开放式)
 $538万
 $27,190/呎
-(18年-07月-02日)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -35941,7 +35941,7 @@
           <t>E | 308呎 (1房)
 $866万
 $28,124/呎
-(18年-07月-18日)</t>
+(18年-07月-19日)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -35949,7 +35949,7 @@
           <t>F | 253呎 (1房)
 $633万
 $25,006/呎
-(18年-06月-26日)</t>
+(18年-06月-27日)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -35957,7 +35957,7 @@
           <t>G | 194呎 (开放式)
 $485万
 $24,999/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -35965,7 +35965,7 @@
           <t>H | 249呎 (1房)
 $592万
 $23,758/呎
-(18年-07月-09日)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -35973,7 +35973,7 @@
           <t>J | 249呎 (1房)
 $607万
 $24,376/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr">
@@ -35981,7 +35981,7 @@
           <t>K | 278呎 (1房)
 $715万
 $25,705/呎
-(18年-07月-02日)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -35989,7 +35989,7 @@
           <t>L | 193呎 (开放式)
 $516万
 $26,716/呎
-(18年-07月-02日)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
     </row>
@@ -36004,7 +36004,7 @@
           <t>A | 417呎 (2房)
 $1051万
 $25,194/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -36012,7 +36012,7 @@
           <t>B | 251呎 (1房)
 $617万
 $24,583/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -36020,7 +36020,7 @@
           <t>C | 252呎 (1房)
 $630万
 $25,002/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -36028,7 +36028,7 @@
           <t>D | 197呎 (开放式)
 $529万
 $26,856/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -36036,7 +36036,7 @@
           <t>E | 307呎 (1房)
 $869万
 $28,305/呎
-(18年-08月-20日)</t>
+(18年-08月-21日)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -36044,7 +36044,7 @@
           <t>F | 253呎 (1房)
 $622万
 $24,584/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -36052,7 +36052,7 @@
           <t>G | 194呎 (开放式)
 $507万
 $26,139/呎
-(18年-06月-25日)</t>
+(18年-06月-26日)</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -36060,7 +36060,7 @@
           <t>H | 248呎 (1房)
 $594万
 $23,942/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
@@ -36068,7 +36068,7 @@
           <t>J | 249呎 (1房)
 $622万
 $24,976/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="K14" s="21" t="inlineStr">
@@ -36076,7 +36076,7 @@
           <t>K | 278呎 (1房)
 $710万
 $25,527/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -36084,7 +36084,7 @@
           <t>L | 193呎 (开放式)
 $507万
 $26,260/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -36099,7 +36099,7 @@
           <t>A | 417呎 (2房)
 $994万
 $23,834/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -36107,7 +36107,7 @@
           <t>B | 251呎 (1房)
 $619万
 $24,673/呎
-(18年-06月-24日)</t>
+(18年-06月-25日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -36115,7 +36115,7 @@
           <t>C | 252呎 (1房)
 $626万
 $24,830/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -36123,7 +36123,7 @@
           <t>D | 198呎 (开放式)
 $525万
 $26,533/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -36131,7 +36131,7 @@
           <t>E | 308呎 (1房)
 $812万
 $26,366/呎
-(18年-06月-22日)</t>
+(18年-06月-23日)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -36139,7 +36139,7 @@
           <t>F | 253呎 (1房)
 $624万
 $24,679/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -36147,7 +36147,7 @@
           <t>G | 194呎 (开放式)
 $484万
 $24,925/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -36155,7 +36155,7 @@
           <t>H | 249呎 (1房)
 $584万
 $23,437/呎
-(18年-06月-08日)</t>
+(18年-06月-09日)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -36163,7 +36163,7 @@
           <t>J | 248呎 (1房)
 $599万
 $24,141/呎
-(18年-07月-11日)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -36171,7 +36171,7 @@
           <t>K | 278呎 (1房)
 $712万
 $25,620/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -36179,7 +36179,7 @@
           <t>L | 193呎 (开放式)
 $503万
 $26,083/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
     </row>
@@ -36194,7 +36194,7 @@
           <t>A | 417呎 (2房)
 $977万
 $23,424/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -36202,7 +36202,7 @@
           <t>B | 251呎 (1房)
 $609万
 $24,250/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -36210,7 +36210,7 @@
           <t>C | 252呎 (1房)
 $694万
 $27,543/呎
-(18年-07月-29日)</t>
+(18年-07月-30日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -36218,7 +36218,7 @@
           <t>D | 198呎 (开放式)
 $538万
 $27,178/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -36226,7 +36226,7 @@
           <t>E | 307呎 (1房)
 $815万
 $26,542/呎
-(18年-07月-18日)</t>
+(18年-07月-19日)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -36234,7 +36234,7 @@
           <t>F | 253呎 (1房)
 $620万
 $24,512/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -36242,7 +36242,7 @@
           <t>G | 194呎 (开放式)
 $490万
 $25,278/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -36250,7 +36250,7 @@
           <t>H | 249呎 (1房)
 $580万
 $23,273/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
@@ -36258,7 +36258,7 @@
           <t>J | 249呎 (1房)
 $601万
 $24,127/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
@@ -36266,7 +36266,7 @@
           <t>K | 278呎 (1房)
 $667万
 $23,983/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -36274,7 +36274,7 @@
           <t>L | 193呎 (开放式)
 $500万
 $25,911/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
     </row>
@@ -36289,7 +36289,7 @@
           <t>A | 417呎 (2房)
 $1001万
 $23,995/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -36297,7 +36297,7 @@
           <t>B | 251呎 (1房)
 $611万
 $24,337/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -36305,7 +36305,7 @@
           <t>C | 252呎 (1房)
 $611万
 $24,240/呎
-(18年-06月-26日)</t>
+(18年-06月-27日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -36313,7 +36313,7 @@
           <t>D | 198呎 (开放式)
 $523万
 $26,434/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -36321,7 +36321,7 @@
           <t>E | 307呎 (1房)
 $809万
 $26,358/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -36329,7 +36329,7 @@
           <t>F | 253呎 (1房)
 $610万
 $24,099/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -36337,7 +36337,7 @@
           <t>G | 194呎 (开放式)
 $472万
 $24,338/呎
-(18年-06月-08日)</t>
+(18年-06月-09日)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -36345,7 +36345,7 @@
           <t>H | 249呎 (1房)
 $576万
 $23,113/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -36353,7 +36353,7 @@
           <t>J | 249呎 (1房)
 $590万
 $23,712/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="K17" s="21" t="inlineStr">
@@ -36361,7 +36361,7 @@
           <t>K | 278呎 (1房)
 $662万
 $23,814/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -36369,7 +36369,7 @@
           <t>L | 193呎 (开放式)
 $502万
 $26,005/呎
-(18年-07月-11日)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
     </row>
@@ -36384,7 +36384,7 @@
           <t>A | 417呎 (2房)
 $973万
 $23,339/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -36392,7 +36392,7 @@
           <t>B | 251呎 (1房)
 $639万
 $25,461/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -36400,7 +36400,7 @@
           <t>C | 252呎 (1房)
 $615万
 $24,411/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -36408,7 +36408,7 @@
           <t>D | 198呎 (开放式)
 $521万
 $26,337/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -36416,7 +36416,7 @@
           <t>E | 308呎 (1房)
 $795万
 $25,807/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -36424,7 +36424,7 @@
           <t>F | 253呎 (1房)
 $608万
 $24,013/呎
-(18年-06月-08日)</t>
+(18年-06月-09日)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -36432,7 +36432,7 @@
           <t>G | 194呎 (开放式)
 $475万
 $24,510/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -36440,7 +36440,7 @@
           <t>H | 249呎 (1房)
 $580万
 $23,275/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
@@ -36448,7 +36448,7 @@
           <t>J | 249呎 (1房)
 $588万
 $23,628/呎
-(18年-06月-24日)</t>
+(18年-06月-25日)</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -36456,7 +36456,7 @@
           <t>K | 278呎 (1房)
 $660万
 $23,731/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -36464,7 +36464,7 @@
           <t>L | 193呎 (开放式)
 $498万
 $25,825/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
     </row>
@@ -36479,7 +36479,7 @@
           <t>A | 417呎 (2房)
 $953万
 $22,852/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -36487,7 +36487,7 @@
           <t>B | 251呎 (1房)
 $652万
 $25,988/呎
-(18年-06月-15日)</t>
+(18年-06月-16日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -36495,7 +36495,7 @@
           <t>C | 252呎 (1房)
 $611万
 $24,244/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -36503,7 +36503,7 @@
           <t>D | 198呎 (开放式)
 $518万
 $26,148/呎
-(18年-06月-27日)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -36511,7 +36511,7 @@
           <t>E | 308呎 (1房)
 $794万
 $25,795/呎
-(18年-06月-15日)</t>
+(18年-06月-16日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -36519,7 +36519,7 @@
           <t>F | 253呎 (1房)
 $610万
 $24,102/呎
-(18年-06月-27日)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -36527,7 +36527,7 @@
           <t>G | 194呎 (开放式)
 $482万
 $24,849/呎
-(18年-06月-27日)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -36535,7 +36535,7 @@
           <t>H | 249呎 (1房)
 $570万
 $22,872/呎
-(18年-06月-26日)</t>
+(18年-06月-27日)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">
@@ -36543,7 +36543,7 @@
           <t>J | 248呎 (1房)
 $582万
 $23,474/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
@@ -36551,7 +36551,7 @@
           <t>K | 278呎 (1房)
 $650万
 $23,396/呎
-(18年-06月-27日)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -36559,7 +36559,7 @@
           <t>L | 193呎 (开放式)
 $505万
 $26,181/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
     </row>
@@ -36574,7 +36574,7 @@
           <t>A | 417呎 (2房)
 $953万
 $22,847/呎
-(18年-06月-08日)</t>
+(18年-06月-09日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -36582,7 +36582,7 @@
           <t>B | 251呎 (1房)
 $626万
 $24,927/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -36590,7 +36590,7 @@
           <t>C | 252呎 (1房)
 $607万
 $24,072/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -36598,7 +36598,7 @@
           <t>D | 198呎 (开放式)
 $509万
 $25,688/呎
-(18年-07月-02日)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -36606,7 +36606,7 @@
           <t>E | 308呎 (1房)
 $741万
 $24,050/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -36614,7 +36614,7 @@
           <t>F | 253呎 (1房)
 $599万
 $23,690/呎
-(18年-06月-27日)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -36622,7 +36622,7 @@
           <t>G | 194呎 (开放式)
 $479万
 $24,682/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -36630,7 +36630,7 @@
           <t>H | 249呎 (1房)
 $566万
 $22,712/呎
-(18年-06月-25日)</t>
+(18年-06月-26日)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -36638,7 +36638,7 @@
           <t>J | 248呎 (1房)
 $576万
 $23,225/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
@@ -36646,7 +36646,7 @@
           <t>K | 278呎 (1房)
 $641万
 $23,061/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -36654,7 +36654,7 @@
           <t>L | 193呎 (开放式)
 $486万
 $25,202/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
     </row>
@@ -36669,7 +36669,7 @@
           <t>A | 417呎 (2房)
 $936万
 $22,445/呎
-(18年-06月-26日)</t>
+(18年-06月-27日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -36677,7 +36677,7 @@
           <t>B | 251呎 (1房)
 $603万
 $24,030/呎
-(18年-06月-25日)</t>
+(18年-06月-26日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -36685,7 +36685,7 @@
           <t>C | 252呎 (1房)
 $594万
 $23,573/呎
-(18年-07月-02日)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -36693,7 +36693,7 @@
           <t>D | 198呎 (开放式)
 $508万
 $25,678/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -36701,7 +36701,7 @@
           <t>E | 307呎 (1房)
 $735万
 $23,950/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -36709,7 +36709,7 @@
           <t>F | 253呎 (1房)
 $595万
 $23,528/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -36717,7 +36717,7 @@
           <t>G | 194呎 (开放式)
 $461万
 $23,760/呎
-(18年-06月-08日)</t>
+(18年-06月-09日)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -36725,7 +36725,7 @@
           <t>H | 249呎 (1房)
 $562万
 $22,552/呎
-(18年-06月-27日)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -36733,7 +36733,7 @@
           <t>J | 249呎 (1房)
 $590万
 $23,685/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="K21" s="21" t="inlineStr">
@@ -36741,7 +36741,7 @@
           <t>K | 278呎 (1房)
 $636万
 $22,895/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -36749,7 +36749,7 @@
           <t>L | 193呎 (开放式)
 $483万
 $25,030/呎
-(18年-06月-25日)</t>
+(18年-06月-26日)</t>
         </is>
       </c>
     </row>
@@ -36764,7 +36764,7 @@
           <t>A | 417呎 (2房)
 $929万
 $22,281/呎
-(18年-06月-27日)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -36772,7 +36772,7 @@
           <t>B | 251呎 (1房)
 $599万
 $23,856/呎
-(18年-06月-26日)</t>
+(18年-06月-27日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -36780,7 +36780,7 @@
           <t>C | 252呎 (1房)
 $588万
 $23,324/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -36788,7 +36788,7 @@
           <t>D | 198呎 (开放式)
 $498万
 $25,127/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -36796,7 +36796,7 @@
           <t>E | 308呎 (1房)
 $722万
 $23,451/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -36804,7 +36804,7 @@
           <t>F | 253呎 (1房)
 $591万
 $23,367/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -36812,7 +36812,7 @@
           <t>G | 194呎 (开放式)
 $458万
 $23,593/呎
-(18年-06月-27日)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -36820,7 +36820,7 @@
           <t>H | 249呎 (1房)
 $558万
 $22,392/呎
-(18年-06月-08日)</t>
+(18年-06月-09日)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -36828,7 +36828,7 @@
           <t>J | 249呎 (1房)
 $574万
 $23,036/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="K22" s="21" t="inlineStr">
@@ -36836,7 +36836,7 @@
           <t>K | 278呎 (1房)
 $625万
 $22,492/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
@@ -36844,7 +36844,7 @@
           <t>L | 193呎 (开放式)
 $490万
 $25,376/呎
-(18年-06月-08日)</t>
+(18年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -36859,7 +36859,7 @@
           <t>A | 417呎 (2房)
 $932万
 $22,352/呎
-(18年-06月-20日)</t>
+(18年-06月-21日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -36867,7 +36867,7 @@
           <t>B | 251呎 (1房)
 $594万
 $23,682/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -36875,7 +36875,7 @@
           <t>C | 252呎 (1房)
 $590万
 $23,402/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -36883,7 +36883,7 @@
           <t>D | 198呎 (开放式)
 $494万
 $24,940/呎
-(18年-06月-27日)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -36891,7 +36891,7 @@
           <t>E | 308呎 (1房)
 $717万
 $23,275/呎
-(18年-10月-10日)</t>
+(18年-10月-11日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -36899,7 +36899,7 @@
           <t>F | 253呎 (1房)
 $587万
 $23,202/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -36907,7 +36907,7 @@
           <t>G | 194呎 (开放式)
 $455万
 $23,432/呎
-(18年-06月-24日)</t>
+(18年-06月-25日)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -36915,7 +36915,7 @@
           <t>H | 248呎 (1房)
 $559万
 $22,556/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -36923,7 +36923,7 @@
           <t>J | 249呎 (1房)
 $564万
 $22,632/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="K23" s="21" t="inlineStr">
@@ -36931,7 +36931,7 @@
           <t>K | 278呎 (1房)
 $621万
 $22,325/呎
-(18年-06月-21日)</t>
+(18年-06月-22日)</t>
         </is>
       </c>
       <c r="L23" s="21" t="inlineStr">
@@ -36939,7 +36939,7 @@
           <t>L | 193呎 (开放式)
 $469万
 $24,326/呎
-(18年-06月-08日)</t>
+(18年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -36954,7 +36954,7 @@
           <t>A | 417呎 (2房)
 $925万
 $22,186/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -36962,7 +36962,7 @@
           <t>B | 251呎 (1房)
 $596万
 $23,759/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -36970,7 +36970,7 @@
           <t>C | 252呎 (1房)
 $585万
 $23,230/呎
-(18年-07月-02日)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -36978,7 +36978,7 @@
           <t>D | 198呎 (开放式)
 $495万
 $25,013/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -36986,7 +36986,7 @@
           <t>E | 308呎 (1房)
 $719万
 $23,342/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -36994,7 +36994,7 @@
           <t>F | 253呎 (1房)
 $583万
 $23,040/呎
-(18年-07月-02日)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -37002,7 +37002,7 @@
           <t>G | 194呎 (开放式)
 $456万
 $23,510/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -37010,7 +37010,7 @@
           <t>H | 249呎 (1房)
 $550万
 $22,071/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -37018,7 +37018,7 @@
           <t>J | 249呎 (1房)
 $565万
 $22,701/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="K24" s="21" t="inlineStr">
@@ -37026,7 +37026,7 @@
           <t>K | 278呎 (1房)
 $636万
 $22,861/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="L24" s="21" t="inlineStr">
@@ -37034,7 +37034,7 @@
           <t>L | 193呎 (开放式)
 $459万
 $23,794/呎
-(18年-06月-25日)</t>
+(18年-06月-26日)</t>
         </is>
       </c>
     </row>
@@ -37049,7 +37049,7 @@
           <t>A | 417呎 (2房)
 $941万
 $22,566/呎
-(18年-06月-25日)</t>
+(18年-06月-26日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -37057,7 +37057,7 @@
           <t>B | 251呎 (1房)
 $594万
 $23,671/呎
-(18年-06月-25日)</t>
+(18年-06月-26日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -37065,7 +37065,7 @@
           <t>C | 252呎 (1房)
 $595万
 $23,629/呎
-(18年-07月-02日)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -37073,7 +37073,7 @@
           <t>D | 198呎 (开放式)
 $488万
 $24,657/呎
-(18年-06月-08日)</t>
+(18年-06月-09日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -37081,7 +37081,7 @@
           <t>E | 308呎 (1房)
 $709万
 $23,010/呎
-(18年-06月-27日)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -37089,7 +37089,7 @@
           <t>F | 253呎 (1房)
 $581万
 $22,961/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -37097,7 +37097,7 @@
           <t>G | 194呎 (开放式)
 $450万
 $23,182/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -37105,7 +37105,7 @@
           <t>H | 248呎 (1房)
 $548万
 $22,080/呎
-(18年-06月-08日)</t>
+(18年-06月-09日)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">
@@ -37113,7 +37113,7 @@
           <t>J | 249呎 (1房)
 $575万
 $23,087/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="K25" s="21" t="inlineStr">
@@ -37121,7 +37121,7 @@
           <t>K | 278呎 (1房)
 $620万
 $22,308/呎
-(18年-07月-02日)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="L25" s="21" t="inlineStr">
@@ -37129,7 +37129,7 @@
           <t>L | 193呎 (开放式)
 $458万
 $23,706/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
     </row>
@@ -37144,7 +37144,7 @@
           <t>A | 417呎 (2房)
 $911万
 $21,857/呎
-(18年-06月-08日)</t>
+(18年-06月-09日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -37152,7 +37152,7 @@
           <t>B | 251呎 (1房)
 $584万
 $23,254/呎
-(18年-06月-24日)</t>
+(18年-06月-25日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -37160,7 +37160,7 @@
           <t>C | 252呎 (1房)
 $573万
 $22,740/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -37168,7 +37168,7 @@
           <t>D | 198呎 (开放式)
 $490万
 $24,727/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -37176,7 +37176,7 @@
           <t>E | 308呎 (1房)
 $711万
 $23,077/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -37184,7 +37184,7 @@
           <t>F | 253呎 (1房)
 $577万
 $22,800/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -37192,7 +37192,7 @@
           <t>G | 194呎 (开放式)
 $446万
 $23,015/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -37200,7 +37200,7 @@
           <t>H | 249呎 (1房)
 $588万
 $23,609/呎
-(18年-07月-02日)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
@@ -37208,7 +37208,7 @@
           <t>J | 249呎 (1房)
 $553万
 $22,216/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="K26" s="21" t="inlineStr">
@@ -37216,7 +37216,7 @@
           <t>K | 278呎 (1房)
 $646万
 $23,248/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="L26" s="21" t="inlineStr">
@@ -37224,7 +37224,7 @@
           <t>L | 193呎 (开放式)
 $496万
 $25,716/呎
-(18年-07月-17日)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
     </row>
@@ -37239,7 +37239,7 @@
           <t>A | 417呎 (2房)
 $920万
 $22,061/呎
-(18年-07月-09日)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -37247,7 +37247,7 @@
           <t>B | 251呎 (1房)
 $595万
 $23,719/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -37255,7 +37255,7 @@
           <t>C | 252呎 (1房)
 $567万
 $22,491/呎
-(18年-07月-08日)</t>
+(18年-07月-09日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -37263,7 +37263,7 @@
           <t>D | 198呎 (开放式)
 $479万
 $24,196/呎
-(18年-06月-28日)</t>
+(18年-06月-29日)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -37271,7 +37271,7 @@
           <t>E | 308呎 (1房)
 $717万
 $23,285/呎
-(18年-06月-08日)</t>
+(18年-06月-09日)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -37279,7 +37279,7 @@
           <t>F | 253呎 (1房)
 $578万
 $22,839/呎
-(18年-07月-03日)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -37287,7 +37287,7 @@
           <t>G | 194呎 (开放式)
 $442万
 $22,771/呎
-(18年-06月-08日)</t>
+(18年-06月-09日)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -37295,7 +37295,7 @@
           <t>H | 249呎 (1房)
 $587万
 $23,591/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -37303,7 +37303,7 @@
           <t>J | 248呎 (1房)
 $548万
 $22,091/呎
-(18年-07月-02日)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="K27" s="21" t="inlineStr">
@@ -37311,7 +37311,7 @@
           <t>K | 278呎 (1房)
 $646万
 $23,226/呎
-(18年-07月-05日)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -37319,7 +37319,7 @@
           <t>L | 193呎 (开放式)
 $491万
 $25,428/呎
-(18年-07月-10日)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
     </row>
@@ -37334,7 +37334,7 @@
           <t>A | 379呎 (2房)
 $1170万
 $30,872/呎
-(19年-11月-03日)</t>
+(19年-11月-04日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -37342,7 +37342,7 @@
           <t>B | 230呎 (1房)
 $700万
 $30,451/呎
-(21年-08月-02日)</t>
+(21年-08月-03日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -37350,7 +37350,7 @@
           <t>C | 230呎 (1房)
 $721万
 $31,359/呎
-(21年-08月-19日)</t>
+(21年-08月-20日)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -37358,7 +37358,7 @@
           <t>D | 175呎 (开放式)
 $398万
 $22,743/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -37366,7 +37366,7 @@
           <t>E | 286呎 (1房)
 $700万
 $24,476/呎
-(24年-04月-04日)</t>
+(24年-04月-05日)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -37374,7 +37374,7 @@
           <t>F | 233呎 (1房)
 $628万
 $26,953/呎
-(23年-03月-15日)</t>
+(23年-03月-16日)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -37382,7 +37382,7 @@
           <t>G | 171呎 (开放式)
 $450万
 $26,316/呎
-(24年-04月-04日)</t>
+(24年-04月-05日)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -37390,7 +37390,7 @@
           <t>H | 227呎 (1房)
 $693万
 $30,521/呎
-(21年-09月-16日)</t>
+(21年-09月-17日)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">
@@ -37398,7 +37398,7 @@
           <t>J | 227呎 (1房)
 $716万
 $31,522/呎
-(18年-08月-06日)</t>
+(18年-08月-07日)</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
@@ -37406,7 +37406,7 @@
           <t>K | 257呎 (1房)
 $720万
 $28,016/呎
-(23年-04月-20日)</t>
+(23年-04月-21日)</t>
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr">
@@ -37414,7 +37414,7 @@
           <t>L | 171呎 (开放式)
 $380万
 $22,222/呎
-(25年-09月-02日)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
     </row>
